--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Swallowing screening Procedure aligned with build_swallowing_screening_procedure().</t>
+    <t>Procedure profile for swallowing screening, including screening type, not-done reason, performer role and timing context.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -671,7 +671,7 @@
 </t>
   </si>
   <si>
-    <t>Reason for current status</t>
+    <t>Reason screening was not done</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -726,7 +726,7 @@
 </t>
   </si>
   <si>
-    <t>Identification of the procedure</t>
+    <t>Swallowing screening type</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -761,10 +761,10 @@
 </t>
   </si>
   <si>
-    <t>Individual or entity the procedure was performed on</t>
-  </si>
-  <si>
-    <t>On whom or on what the procedure was performed. This is usually an individual human, but can also be performed on animals, groups of humans or animals, organizations or practitioners (for licensing), locations or devices (for safety inspections or regulatory authorizations).  If the actual focus of the procedure is different from the subject, the focus element specifies the actual focus of the procedure.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -799,10 +799,10 @@
 </t>
   </si>
   <si>
-    <t>The Encounter during which this Procedure was created</t>
-  </si>
-  <si>
-    <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
@@ -926,7 +926,7 @@
 </t>
   </si>
   <si>
-    <t>Who performed the procedure and what they did</t>
+    <t>Screening performer</t>
   </si>
   <si>
     <t>Indicates who or what performed the procedure and how they were involved.</t>
@@ -1580,98 +1580,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1857,10 +1859,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1940,7 +1942,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}stroke-swallow-completed-requires-post-acute-care:If the swallowing screening procedure is completed, post-acute care required extension SHALL be present. {status != 'completed' or extension.where(url = 'http://tecnomod-um.org/StructureDefinition/post-acute-care-required-ext').exists()}stroke-swallow-not-done-requires-status-reason:If the swallowing screening procedure was not done, statusReason SHALL be present. {status != 'not-done' or statusReason.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>88</v>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/stroke-swallow-procedure-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/stroke-swallow-procedure-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}stroke-swallow-completed-requires-post-acute-care:If the swallowing screening procedure is completed, post-acute care required extension SHALL be present. {status != 'completed' or extension.where(url = 'http://tecnomod-um.org/StructureDefinition/post-acute-care-required-ext').exists()}stroke-swallow-not-done-requires-status-reason:If the swallowing screening procedure was not done, statusReason SHALL be present. {status != 'not-done' or statusReason.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}stroke-swallow-completed-requires-post-acute-care:If the swallowing screening procedure is completed, post-acute care required extension SHALL be present. {status != 'completed' or extension.where(url = 'http://qualityregistry.org/StructureDefinition/post-acute-care-required-ext').exists()}stroke-swallow-not-done-requires-status-reason:If the swallowing screening procedure was not done, statusReason SHALL be present. {status != 'not-done' or statusReason.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -466,7 +466,7 @@
     <t>procedureTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/procedure-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/procedure-timing-context-ext}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>postAcuteCareRequired</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/post-acute-care-required-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/post-acute-care-required-ext}
 </t>
   </si>
   <si>
@@ -683,7 +683,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/procedure-not-done-reason-vs</t>
+    <t>http://qualityregistry.org/ValueSet/procedure-not-done-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -735,7 +735,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/swallowing-screening-type-vs</t>
+    <t>http://qualityregistry.org/ValueSet/swallowing-screening-type-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -757,7 +757,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -795,7 +795,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>
@@ -1024,7 +1024,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-practitioner-role-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-practitioner-role-profile)
 </t>
   </si>
   <si>
@@ -1719,7 +1719,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.79296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.2421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-swallow-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-swallow-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
